--- a/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C99B559-B5CB-4DB3-BE48-02EF301EFE63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA07B03-BAC3-4FD1-B9ED-A158D8CAF216}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E0BACE-30F3-4A4F-8E41-2BDA332CF502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E24982F1-74C4-4D5C-95CB-5FD8F2F891D3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFD7E637-A609-4223-83F6-66E8B8A69480}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0434DBE3-1885-4D46-8EC6-49F8584BB0FE}"/>
 </file>